--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.24014405314408</v>
+        <v>8.976523408635913</v>
       </c>
       <c r="D2" t="n">
-        <v>56.47685639608873</v>
+        <v>9.17748916436442</v>
       </c>
       <c r="E2" t="n">
-        <v>23.49460951252131</v>
+        <v>3.817874045784714</v>
       </c>
       <c r="F2" t="n">
-        <v>24.09922727342248</v>
+        <v>3.916124431931153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.250925028101451</v>
+        <v>1.340775317066486</v>
       </c>
       <c r="D3" t="n">
-        <v>8.278401849243778</v>
+        <v>1.345240300502114</v>
       </c>
       <c r="E3" t="n">
-        <v>23.49460951252131</v>
+        <v>3.817874045784714</v>
       </c>
       <c r="F3" t="n">
-        <v>24.09922727342248</v>
+        <v>3.916124431931153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
